--- a/reports/telegram/aegis_daily_2026-08-14.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-14.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ADSK_USA_20260814</t>
+          <t>MU_USA_20260814</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -806,7 +806,7 @@
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="n">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="O2" s="3" t="n">
-        <v>59.1</v>
+        <v>53.5</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
@@ -826,12 +826,12 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 59% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 54% · band HOLD · 60d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="n">
-        <v>59.1</v>
+        <v>54.3</v>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="V2" s="3" t="n">
-        <v>31.4</v>
+        <v>34.2</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>1</v>
@@ -848,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
@@ -859,40 +859,40 @@
         </is>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>257.96</v>
+        <v>964.29</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>257.96</v>
+        <v>964.29</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>255.38</v>
+        <v>954.65</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>260.54</v>
+        <v>973.9299999999999</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>242.48</v>
+        <v>906.4299999999999</v>
       </c>
       <c r="AG2" s="3" t="n">
         <v>-6</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>288.92</v>
+        <v>1080</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>319.87</v>
+        <v>1195.72</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>24</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>249.51</v>
+        <v>949.83</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>3.39</v>
+        <v>1.52</v>
       </c>
       <c r="AN2" s="3" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AQ2" s="3" t="inlineStr">
         <is>
-          <t>Growth · Trend · Value</t>
+          <t>Growth · Quality · Mean Reversion</t>
         </is>
       </c>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -917,14 +917,14 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260814</t>
+          <t>ADSK_USA_20260814</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -961,7 +961,7 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="O3" s="3" t="n">
-        <v>52.9</v>
+        <v>58.3</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -981,12 +981,12 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 53% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 59% · band HOLD · 22d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="n">
-        <v>52.9</v>
+        <v>59.1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="V3" s="3" t="n">
-        <v>31.1</v>
+        <v>31.6</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>1</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>179.01</v>
+        <v>253.21</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>179.01</v>
+        <v>253.21</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>177.22</v>
+        <v>250.67</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>180.8</v>
+        <v>255.74</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>168.27</v>
+        <v>238.01</v>
       </c>
       <c r="AG3" s="3" t="n">
         <v>-6</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>200.49</v>
+        <v>283.59</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>221.97</v>
+        <v>313.97</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>24</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>171.04</v>
+        <v>257.96</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>4.66</v>
+        <v>-1.84</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>Value · Quality · Growth</t>
+          <t>Growth · Trend · Value</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1072,14 +1072,14 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EIX_USA_20260814</t>
+          <t>FOXA_USA_20260814</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="n">
-        <v>65.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="O4" s="5" t="n">
-        <v>62.2</v>
+        <v>58.3</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 62% · band HOLD · 17d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 59% · band HOLD · 22d left · → BUY</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="n">
-        <v>62.2</v>
+        <v>59.1</v>
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="V4" s="5" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="W4" s="5" t="n">
         <v>1</v>
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Z4" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AA4" s="5" t="inlineStr">
         <is>
@@ -1169,40 +1169,40 @@
         </is>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>70.68000000000001</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>70.68000000000001</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="AD4" s="5" t="n">
-        <v>69.97</v>
+        <v>68.38</v>
       </c>
       <c r="AE4" s="5" t="n">
-        <v>71.39</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="AF4" s="5" t="n">
-        <v>66.44</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="AG4" s="5" t="n">
-        <v>-6</v>
+        <v>-5.99</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>79.16</v>
+        <v>77.36</v>
       </c>
       <c r="AI4" s="5" t="n">
         <v>12</v>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>87.64</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="AK4" s="5" t="n">
         <v>24</v>
       </c>
       <c r="AL4" s="5" t="n">
-        <v>69.40000000000001</v>
+        <v>65.45</v>
       </c>
       <c r="AM4" s="5" t="n">
-        <v>1.84</v>
+        <v>5.53</v>
       </c>
       <c r="AN4" s="5" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AQ4" s="5" t="inlineStr">
         <is>
-          <t>Mean Reversion · Value · Event Driven</t>
+          <t>Event Driven · Trend · Mean Reversion</t>
         </is>
       </c>
       <c r="AR4" s="5" t="inlineStr"/>
@@ -1227,14 +1227,14 @@
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>BMY_USA_20260814</t>
+          <t>TER_USA_20260814</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="n">
-        <v>77.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="O5" s="7" t="n">
-        <v>58.9</v>
+        <v>58.2</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 59% · band HOLD · 17d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 59% · band HOLD · 22d left · → HOLD</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AA5" s="7" t="inlineStr">
         <is>
@@ -1324,40 +1324,40 @@
         </is>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>64.65000000000001</v>
+        <v>402.01</v>
       </c>
       <c r="AC5" s="7" t="n">
-        <v>64.65000000000001</v>
+        <v>402.01</v>
       </c>
       <c r="AD5" s="7" t="n">
-        <v>64</v>
+        <v>397.99</v>
       </c>
       <c r="AE5" s="7" t="n">
-        <v>65.3</v>
+        <v>406.03</v>
       </c>
       <c r="AF5" s="7" t="n">
-        <v>61.42</v>
+        <v>381.91</v>
       </c>
       <c r="AG5" s="7" t="n">
         <v>-5</v>
       </c>
       <c r="AH5" s="7" t="n">
-        <v>69.81999999999999</v>
+        <v>434.17</v>
       </c>
       <c r="AI5" s="7" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" s="7" t="n">
-        <v>74.34999999999999</v>
+        <v>462.31</v>
       </c>
       <c r="AK5" s="7" t="n">
         <v>15</v>
       </c>
       <c r="AL5" s="7" t="n">
-        <v>63.7</v>
+        <v>410.52</v>
       </c>
       <c r="AM5" s="7" t="n">
-        <v>1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AN5" s="7" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AQ5" s="7" t="inlineStr">
         <is>
-          <t>Growth · Trend · Event Driven</t>
+          <t>Growth · Quality · Mean Reversion</t>
         </is>
       </c>
       <c r="AR5" s="7" t="inlineStr"/>
@@ -1380,14 +1380,14 @@
       </c>
       <c r="AU5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>UBER_USA_20260814</t>
+          <t>PLTR_USA_20260814</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
       <c r="M6" s="7" t="n">
-        <v>68.7</v>
+        <v>74.7</v>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="O6" s="7" t="n">
-        <v>62.2</v>
+        <v>52.1</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 62% · band HOLD · 17d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 53% · band HOLD · 20d left · → HOLD</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr"/>
       <c r="T6" s="7" t="n">
-        <v>62.2</v>
+        <v>52.9</v>
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="V6" s="7" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="W6" s="7" t="n">
         <v>1</v>
@@ -1466,10 +1466,10 @@
         <v>0</v>
       </c>
       <c r="Y6" s="7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z6" s="7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA6" s="7" t="inlineStr">
         <is>
@@ -1477,40 +1477,40 @@
         </is>
       </c>
       <c r="AB6" s="7" t="n">
-        <v>75.88</v>
+        <v>177.06</v>
       </c>
       <c r="AC6" s="7" t="n">
-        <v>75.88</v>
+        <v>177.06</v>
       </c>
       <c r="AD6" s="7" t="n">
-        <v>75.12</v>
+        <v>175.29</v>
       </c>
       <c r="AE6" s="7" t="n">
-        <v>76.64</v>
+        <v>178.83</v>
       </c>
       <c r="AF6" s="7" t="n">
-        <v>72.09</v>
+        <v>168.21</v>
       </c>
       <c r="AG6" s="7" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
       <c r="AH6" s="7" t="n">
-        <v>81.95</v>
+        <v>191.22</v>
       </c>
       <c r="AI6" s="7" t="n">
         <v>8</v>
       </c>
       <c r="AJ6" s="7" t="n">
-        <v>87.26000000000001</v>
+        <v>203.62</v>
       </c>
       <c r="AK6" s="7" t="n">
         <v>15</v>
       </c>
       <c r="AL6" s="7" t="n">
-        <v>75.36</v>
+        <v>179.01</v>
       </c>
       <c r="AM6" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="AN6" s="7" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AQ6" s="7" t="inlineStr">
         <is>
-          <t>Event Driven · Growth · Quality</t>
+          <t>Value · Quality · Growth</t>
         </is>
       </c>
       <c r="AR6" s="7" t="inlineStr"/>
@@ -1533,783 +1533,813 @@
       </c>
       <c r="AU6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>TER_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>SAIC_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>TER</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="n">
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>→ MU · +5.1pp alpha</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O7" s="7" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="O7" s="9" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 59% · band HOLD · 17d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr"/>
-      <c r="T7" s="7" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #6 · Conf 59% · band HOLD · 22d left · → EXIT (rotate to MU)</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr"/>
+      <c r="T7" s="9" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="U7" s="9" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V7" s="7" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="W7" s="7" t="n">
+      <c r="V7" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="W7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z7" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA7" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" s="7" t="n">
-        <v>410.52</v>
-      </c>
-      <c r="AC7" s="7" t="n">
-        <v>410.52</v>
-      </c>
-      <c r="AD7" s="7" t="n">
-        <v>406.41</v>
-      </c>
-      <c r="AE7" s="7" t="n">
-        <v>414.63</v>
-      </c>
-      <c r="AF7" s="7" t="n">
-        <v>389.99</v>
-      </c>
-      <c r="AG7" s="7" t="n">
+      <c r="X7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB7" s="9" t="n">
+        <v>125.89</v>
+      </c>
+      <c r="AC7" s="9" t="n">
+        <v>125.89</v>
+      </c>
+      <c r="AD7" s="9" t="n">
+        <v>124.63</v>
+      </c>
+      <c r="AE7" s="9" t="n">
+        <v>127.15</v>
+      </c>
+      <c r="AF7" s="9" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="AG7" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="AH7" s="7" t="n">
-        <v>443.36</v>
-      </c>
-      <c r="AI7" s="7" t="n">
+      <c r="AH7" s="9" t="n">
+        <v>135.96</v>
+      </c>
+      <c r="AI7" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AJ7" s="7" t="n">
-        <v>472.1</v>
-      </c>
-      <c r="AK7" s="7" t="n">
+      <c r="AJ7" s="9" t="n">
+        <v>144.77</v>
+      </c>
+      <c r="AK7" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AL7" s="7" t="n">
-        <v>402.74</v>
-      </c>
-      <c r="AM7" s="7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AN7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="7" t="inlineStr">
-        <is>
-          <t>Growth · Quality · Mean Reversion</t>
-        </is>
-      </c>
-      <c r="AR7" s="7" t="inlineStr"/>
-      <c r="AS7" s="7" t="inlineStr"/>
-      <c r="AT7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AL7" s="9" t="n">
+        <v>126.66</v>
+      </c>
+      <c r="AM7" s="9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="9" t="inlineStr">
+        <is>
+          <t>Event Driven · Growth · Trend</t>
+        </is>
+      </c>
+      <c r="AR7" s="9" t="inlineStr"/>
+      <c r="AS7" s="9" t="inlineStr"/>
+      <c r="AT7" s="9" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AU7" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>SAIC_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SMCI_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="n">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>→ MU · +5.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr"/>
-      <c r="M8" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="9" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #7 · Conf 56% · band HOLD · 22d left · → EXIT (rotate to MU)</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr"/>
+      <c r="T8" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="P8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 56% · band HOLD · 17d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr"/>
-      <c r="T8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
+      <c r="U8" s="9" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V8" s="7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="W8" s="7" t="n">
+      <c r="V8" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="W8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z8" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA8" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" s="7" t="n">
-        <v>126.66</v>
-      </c>
-      <c r="AC8" s="7" t="n">
-        <v>126.66</v>
-      </c>
-      <c r="AD8" s="7" t="n">
-        <v>125.39</v>
-      </c>
-      <c r="AE8" s="7" t="n">
-        <v>127.93</v>
-      </c>
-      <c r="AF8" s="7" t="n">
-        <v>120.33</v>
-      </c>
-      <c r="AG8" s="7" t="n">
+      <c r="X8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA8" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AC8" s="9" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AD8" s="9" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="AE8" s="9" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="AF8" s="9" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="AG8" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="AH8" s="7" t="n">
-        <v>136.79</v>
-      </c>
-      <c r="AI8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ8" s="7" t="n">
-        <v>145.66</v>
-      </c>
-      <c r="AK8" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL8" s="7" t="n">
-        <v>126.31</v>
-      </c>
-      <c r="AM8" s="7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AN8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="7" t="inlineStr">
-        <is>
-          <t>Event Driven · Trend · Growth</t>
-        </is>
-      </c>
-      <c r="AR8" s="7" t="inlineStr"/>
-      <c r="AS8" s="7" t="inlineStr"/>
-      <c r="AT8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AH8" s="9" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="AI8" s="9" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AJ8" s="9" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AL8" s="9" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="AM8" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="9" t="inlineStr">
+        <is>
+          <t>Event Driven · Momentum · Growth</t>
+        </is>
+      </c>
+      <c r="AR8" s="9" t="inlineStr"/>
+      <c r="AS8" s="9" t="inlineStr"/>
+      <c r="AT8" s="9" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AU8" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>SMCI_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>EIX_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>SMCI</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="n">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>→ MU · +5.4pp alpha</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O9" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="O9" s="9" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #8 · Conf 56% · band HOLD · 17d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr"/>
-      <c r="T9" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #8 · Conf 62% · band HOLD · 22d left · → EXIT (rotate to MU)</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr"/>
+      <c r="T9" s="9" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U9" s="9" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V9" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W9" s="7" t="n">
+      <c r="V9" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z9" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA9" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB9" s="7" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="AC9" s="7" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="AD9" s="7" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="AE9" s="7" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="AF9" s="7" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="AG9" s="7" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="AH9" s="7" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="AI9" s="7" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="AJ9" s="7" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="AK9" s="7" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="AL9" s="7" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="AM9" s="7" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AN9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="7" t="inlineStr">
-        <is>
-          <t>Event Driven · Momentum · Growth</t>
-        </is>
-      </c>
-      <c r="AR9" s="7" t="inlineStr"/>
-      <c r="AS9" s="7" t="inlineStr"/>
-      <c r="AT9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="AC9" s="9" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="AD9" s="9" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="AF9" s="9" t="n">
+        <v>67.53</v>
+      </c>
+      <c r="AG9" s="9" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="AH9" s="9" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="AI9" s="9" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AJ9" s="9" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="AK9" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" s="9" t="n">
+        <v>70.68000000000001</v>
+      </c>
+      <c r="AM9" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="9" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Event Driven</t>
+        </is>
+      </c>
+      <c r="AR9" s="9" t="inlineStr"/>
+      <c r="AS9" s="9" t="inlineStr"/>
+      <c r="AT9" s="9" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AU9" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>CRM_USA_20260814</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Salesforce</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-      <c r="J10" s="7" t="n">
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>→ MU · +5.7pp alpha</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O10" s="7" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="O10" s="9" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 61% · band HOLD · 17d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr"/>
-      <c r="T10" s="7" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #9 · Conf 64% · band HOLD · 22d left · → EXIT (rotate to MU)</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr"/>
+      <c r="T10" s="9" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U10" s="9" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V10" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W10" s="7" t="n">
+      <c r="V10" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z10" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA10" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB10" s="7" t="n">
+      <c r="X10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA10" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>196.66</v>
+      </c>
+      <c r="AC10" s="9" t="n">
+        <v>196.66</v>
+      </c>
+      <c r="AD10" s="9" t="n">
+        <v>194.69</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>198.63</v>
+      </c>
+      <c r="AF10" s="9" t="n">
+        <v>186.83</v>
+      </c>
+      <c r="AG10" s="9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH10" s="9" t="n">
+        <v>212.39</v>
+      </c>
+      <c r="AI10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="9" t="n">
+        <v>226.16</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL10" s="9" t="n">
         <v>201.37</v>
       </c>
-      <c r="AC10" s="7" t="n">
-        <v>201.37</v>
-      </c>
-      <c r="AD10" s="7" t="n">
-        <v>199.36</v>
-      </c>
-      <c r="AE10" s="7" t="n">
-        <v>203.38</v>
-      </c>
-      <c r="AF10" s="7" t="n">
-        <v>191.3</v>
-      </c>
-      <c r="AG10" s="7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH10" s="7" t="n">
-        <v>217.48</v>
-      </c>
-      <c r="AI10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ10" s="7" t="n">
-        <v>231.58</v>
-      </c>
-      <c r="AK10" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL10" s="7" t="n">
-        <v>193.32</v>
-      </c>
-      <c r="AM10" s="7" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AN10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="7" t="inlineStr">
+      <c r="AM10" s="9" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="9" t="inlineStr">
         <is>
           <t>Event Driven · News · Mean Reversion</t>
         </is>
       </c>
-      <c r="AR10" s="7" t="inlineStr"/>
-      <c r="AS10" s="7" t="inlineStr"/>
-      <c r="AT10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AR10" s="9" t="inlineStr"/>
+      <c r="AS10" s="9" t="inlineStr"/>
+      <c r="AT10" s="9" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AU10" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>FOXA_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>UBER_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>FOXA</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="n">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>→ MU · +5.7pp alpha</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr"/>
+      <c r="M11" s="9" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="9" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #10 · Conf 59% · band HOLD · 22d left · → EXIT (rotate to MU)</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr"/>
+      <c r="T11" s="9" t="n">
         <v>59.1</v>
       </c>
-      <c r="P11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 59% · band HOLD · 17d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr"/>
-      <c r="T11" s="7" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
+      <c r="U11" s="9" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V11" s="7" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W11" s="7" t="n">
+      <c r="V11" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z11" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA11" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB11" s="7" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="AC11" s="7" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="AD11" s="7" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="AE11" s="7" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="AF11" s="7" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="AG11" s="7" t="n">
+      <c r="X11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="AC11" s="9" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="AD11" s="9" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="AE11" s="9" t="n">
+        <v>76.17</v>
+      </c>
+      <c r="AF11" s="9" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="AG11" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="AH11" s="7" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="AI11" s="7" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="AJ11" s="7" t="n">
-        <v>75.27</v>
-      </c>
-      <c r="AK11" s="7" t="n">
+      <c r="AH11" s="9" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="AI11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="9" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="AK11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AL11" s="7" t="n">
-        <v>63.05</v>
-      </c>
-      <c r="AM11" s="7" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AN11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="7" t="inlineStr">
-        <is>
-          <t>Event Driven · Value · News</t>
-        </is>
-      </c>
-      <c r="AR11" s="7" t="inlineStr"/>
-      <c r="AS11" s="7" t="inlineStr"/>
-      <c r="AT11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AL11" s="9" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AM11" s="9" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="9" t="inlineStr">
+        <is>
+          <t>Event Driven · Growth · Quality</t>
+        </is>
+      </c>
+      <c r="AR11" s="9" t="inlineStr"/>
+      <c r="AS11" s="9" t="inlineStr"/>
+      <c r="AT11" s="9" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AU11" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>BLDR_USA_20260814</t>
+          <t>AJG_USA_20260814</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -2329,7 +2359,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr"/>
@@ -2340,7 +2370,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>→ ADSK · +57.6pp alpha</t>
+          <t>→ MU · +61.4pp alpha</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
@@ -2352,7 +2382,7 @@
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="9" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
@@ -2360,10 +2390,10 @@
         </is>
       </c>
       <c r="O12" s="9" t="n">
-        <v>32.1</v>
+        <v>35.3</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -2372,12 +2402,12 @@
       </c>
       <c r="R12" s="9" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #11 · Conf 32% · band EXIT · 17d left · → EXIT (rotate to ADSK)</t>
+          <t>🔴 AVOID · Rank #11 · Conf 36% · band EXIT · 60d left · → EXIT (rotate to MU)</t>
         </is>
       </c>
       <c r="S12" s="9" t="inlineStr"/>
       <c r="T12" s="9" t="n">
-        <v>32.1</v>
+        <v>36</v>
       </c>
       <c r="U12" s="9" t="inlineStr">
         <is>
@@ -2385,7 +2415,7 @@
         </is>
       </c>
       <c r="V12" s="9" t="n">
-        <v>-26.2</v>
+        <v>-27.2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>1</v>
@@ -2394,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AA12" s="9" t="inlineStr">
         <is>
@@ -2405,40 +2435,40 @@
         </is>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>73.56</v>
+        <v>252</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>73.56</v>
+        <v>252</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>72.81999999999999</v>
+        <v>249.48</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>74.3</v>
+        <v>254.52</v>
       </c>
       <c r="AF12" s="9" t="n">
-        <v>69.88</v>
+        <v>239.4</v>
       </c>
       <c r="AG12" s="9" t="n">
         <v>-5</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>79.44</v>
+        <v>272.16</v>
       </c>
       <c r="AI12" s="9" t="n">
-        <v>7.99</v>
+        <v>8</v>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>84.59</v>
+        <v>289.8</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="AL12" s="9" t="n">
-        <v>72.41</v>
+        <v>253.49</v>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>1.59</v>
+        <v>-0.59</v>
       </c>
       <c r="AN12" s="9" t="n">
         <v>0</v>
@@ -2451,24 +2481,24 @@
       </c>
       <c r="AQ12" s="9" t="inlineStr">
         <is>
-          <t>Adx 14 · Close · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+          <t>Adx 14 · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close · Distance From 52W High Pct</t>
         </is>
       </c>
       <c r="AR12" s="9" t="inlineStr"/>
       <c r="AS12" s="9" t="inlineStr"/>
       <c r="AT12" s="9" t="n">
-        <v>57.6</v>
+        <v>61.41</v>
       </c>
       <c r="AU12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>TTWO_USA_20260814</t>
+          <t>MOS_USA_20260814</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -2488,7 +2518,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr"/>
@@ -2499,19 +2529,19 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>→ ADSK · +58.4pp alpha</t>
+          <t>→ MU · +62.3pp alpha</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
       <c r="L13" s="9" t="inlineStr"/>
       <c r="M13" s="9" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
@@ -2519,10 +2549,10 @@
         </is>
       </c>
       <c r="O13" s="9" t="n">
-        <v>30</v>
+        <v>30.9</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
@@ -2531,12 +2561,12 @@
       </c>
       <c r="R13" s="9" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #12 · Conf 30% · band EXIT · 17d left · → EXIT (rotate to ADSK)</t>
+          <t>🔴 AVOID · Rank #13 · Conf 32% · band EXIT · 60d left · → EXIT (rotate to MU)</t>
         </is>
       </c>
       <c r="S13" s="9" t="inlineStr"/>
       <c r="T13" s="9" t="n">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="U13" s="9" t="inlineStr">
         <is>
@@ -2544,7 +2574,7 @@
         </is>
       </c>
       <c r="V13" s="9" t="n">
-        <v>-27</v>
+        <v>-28.1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>1</v>
@@ -2553,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AA13" s="9" t="inlineStr">
         <is>
@@ -2564,40 +2594,40 @@
         </is>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>241.91</v>
+        <v>21.82</v>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>241.91</v>
+        <v>21.82</v>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>239.49</v>
+        <v>21.6</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>244.33</v>
+        <v>22.04</v>
       </c>
       <c r="AF13" s="9" t="n">
-        <v>229.81</v>
+        <v>20.73</v>
       </c>
       <c r="AG13" s="9" t="n">
         <v>-5</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>261.26</v>
+        <v>23.57</v>
       </c>
       <c r="AI13" s="9" t="n">
-        <v>8</v>
+        <v>8.02</v>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>278.2</v>
+        <v>25.09</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>15</v>
+        <v>14.99</v>
       </c>
       <c r="AL13" s="9" t="n">
-        <v>243</v>
+        <v>21.78</v>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>-0.45</v>
+        <v>0.16</v>
       </c>
       <c r="AN13" s="9" t="n">
         <v>0</v>
@@ -2610,183 +2640,177 @@
       </c>
       <c r="AQ13" s="9" t="inlineStr">
         <is>
-          <t>Adx 14 · Close · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+          <t>Adx 14 · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close · Distance From 52W High Pct</t>
         </is>
       </c>
       <c r="AR13" s="9" t="inlineStr"/>
       <c r="AS13" s="9" t="inlineStr"/>
       <c r="AT13" s="9" t="n">
-        <v>58.37</v>
+        <v>62.3</v>
       </c>
       <c r="AU13" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>MCK_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PLTR_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>MCK</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>→ ADSK · +59.4pp alpha</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
-      <c r="M14" s="9" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>🔴 AVOID · Rank #13 · Conf 30% · band EXIT · 17d left · → EXIT (rotate to ADSK)</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr"/>
-      <c r="T14" s="9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="U14" s="9" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 53% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>-28</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA14" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB14" s="9" t="n">
-        <v>856.6900000000001</v>
-      </c>
-      <c r="AC14" s="9" t="n">
-        <v>856.6900000000001</v>
-      </c>
-      <c r="AD14" s="9" t="n">
-        <v>848.12</v>
-      </c>
-      <c r="AE14" s="9" t="n">
-        <v>865.26</v>
-      </c>
-      <c r="AF14" s="9" t="n">
-        <v>813.86</v>
-      </c>
-      <c r="AG14" s="9" t="n">
+      <c r="V14" s="5" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>177.06</v>
+      </c>
+      <c r="AC14" s="5" t="n">
+        <v>177.06</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>173.52</v>
+      </c>
+      <c r="AE14" s="5" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>168.207</v>
+      </c>
+      <c r="AG14" s="5" t="n">
         <v>-5</v>
       </c>
-      <c r="AH14" s="9" t="n">
-        <v>925.23</v>
-      </c>
-      <c r="AI14" s="9" t="n">
+      <c r="AH14" s="5" t="n">
+        <v>191.2248</v>
+      </c>
+      <c r="AI14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AJ14" s="9" t="n">
-        <v>985.1900000000001</v>
-      </c>
-      <c r="AK14" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL14" s="9" t="n">
-        <v>878.73</v>
-      </c>
-      <c r="AM14" s="9" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="AN14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="9" t="inlineStr">
-        <is>
-          <t>Adx 14 · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close · Distance From 52W High Pct</t>
-        </is>
-      </c>
-      <c r="AR14" s="9" t="inlineStr"/>
-      <c r="AS14" s="9" t="inlineStr"/>
-      <c r="AT14" s="9" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="AU14" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AJ14" s="5" t="n">
+        <v>204.610536</v>
+      </c>
+      <c r="AK14" s="5" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL14" s="5" t="n">
+        <v>179.01</v>
+      </c>
+      <c r="AM14" s="5" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AN14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="5" t="inlineStr"/>
+      <c r="AR14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT14" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>UBER_USA_20260814</t>
+          <t>MU_USA_20260814</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2806,7 +2830,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -2818,12 +2842,12 @@
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="n">
-        <v>68.7</v>
+        <v>75.8</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -2831,10 +2855,10 @@
         </is>
       </c>
       <c r="O15" s="5" t="n">
-        <v>62.2</v>
+        <v>53.5</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
@@ -2843,12 +2867,12 @@
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 62% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr"/>
       <c r="T15" s="5" t="n">
-        <v>62.2</v>
+        <v>54.3</v>
       </c>
       <c r="U15" s="5" t="inlineStr">
         <is>
@@ -2856,7 +2880,7 @@
         </is>
       </c>
       <c r="V15" s="5" t="n">
-        <v>76.3</v>
+        <v>68.8</v>
       </c>
       <c r="W15" s="5" t="inlineStr"/>
       <c r="X15" s="5" t="n">
@@ -2874,40 +2898,40 @@
         </is>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>75.88</v>
+        <v>964.29</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>75.88</v>
+        <v>964.29</v>
       </c>
       <c r="AD15" s="5" t="n">
-        <v>74.36</v>
+        <v>954.65</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>973.9299999999999</v>
       </c>
       <c r="AF15" s="5" t="n">
-        <v>72.086</v>
+        <v>916.0754999999999</v>
       </c>
       <c r="AG15" s="5" t="n">
         <v>-5</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>81.9504</v>
+        <v>1080</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>87.68692800000001</v>
+        <v>1155.6</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AL15" s="5" t="n">
-        <v>75.36</v>
+        <v>949.83</v>
       </c>
       <c r="AM15" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="AN15" s="5" t="n">
         <v>0</v>
@@ -2928,18 +2952,18 @@
         <v>5</v>
       </c>
       <c r="AT15" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AU15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>EIX_USA_20260814</t>
+          <t>TER_USA_20260814</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2959,7 +2983,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -2971,12 +2995,12 @@
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="n">
-        <v>65.3</v>
+        <v>75.3</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -2984,10 +3008,10 @@
         </is>
       </c>
       <c r="O16" s="5" t="n">
-        <v>62.2</v>
+        <v>58.2</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
@@ -2996,12 +3020,12 @@
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 62% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr"/>
       <c r="T16" s="5" t="n">
-        <v>62.2</v>
+        <v>58.9</v>
       </c>
       <c r="U16" s="5" t="inlineStr">
         <is>
@@ -3009,7 +3033,7 @@
         </is>
       </c>
       <c r="V16" s="5" t="n">
-        <v>74.7</v>
+        <v>68.2</v>
       </c>
       <c r="W16" s="5" t="inlineStr"/>
       <c r="X16" s="5" t="n">
@@ -3027,40 +3051,40 @@
         </is>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>70.68000000000001</v>
+        <v>402.01</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>70.68000000000001</v>
+        <v>402.01</v>
       </c>
       <c r="AD16" s="5" t="n">
-        <v>69.97</v>
+        <v>393.97</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>71.39</v>
+        <v>410.05</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>67.146</v>
+        <v>381.9095</v>
       </c>
       <c r="AG16" s="5" t="n">
         <v>-5</v>
       </c>
       <c r="AH16" s="5" t="n">
-        <v>79.16</v>
+        <v>434.1708</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>84.7012</v>
+        <v>464.5627560000001</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AL16" s="5" t="n">
-        <v>69.40000000000001</v>
+        <v>410.52</v>
       </c>
       <c r="AM16" s="5" t="n">
-        <v>1.84</v>
+        <v>-2.07</v>
       </c>
       <c r="AN16" s="5" t="n">
         <v>0</v>
@@ -3081,18 +3105,18 @@
         <v>5</v>
       </c>
       <c r="AT16" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AU16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260814</t>
+          <t>ADSK_USA_20260814</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -3112,7 +3136,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -3124,12 +3148,12 @@
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="5" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -3137,10 +3161,10 @@
         </is>
       </c>
       <c r="O17" s="5" t="n">
-        <v>52.9</v>
+        <v>58.3</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
@@ -3149,12 +3173,12 @@
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 53% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr"/>
       <c r="T17" s="5" t="n">
-        <v>52.9</v>
+        <v>59.1</v>
       </c>
       <c r="U17" s="5" t="inlineStr">
         <is>
@@ -3162,7 +3186,7 @@
         </is>
       </c>
       <c r="V17" s="5" t="n">
-        <v>69.8</v>
+        <v>62.8</v>
       </c>
       <c r="W17" s="5" t="inlineStr"/>
       <c r="X17" s="5" t="n">
@@ -3180,40 +3204,40 @@
         </is>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>179.01</v>
+        <v>253.21</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>179.01</v>
+        <v>253.21</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>177.22</v>
+        <v>250.67</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>180.8</v>
+        <v>255.74</v>
       </c>
       <c r="AF17" s="5" t="n">
-        <v>170.0595</v>
+        <v>240.5495</v>
       </c>
       <c r="AG17" s="5" t="n">
         <v>-5</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>200.49</v>
+        <v>283.59</v>
       </c>
       <c r="AI17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>214.5243</v>
+        <v>303.4413</v>
       </c>
       <c r="AK17" s="5" t="n">
         <v>19.84</v>
       </c>
       <c r="AL17" s="5" t="n">
-        <v>171.04</v>
+        <v>257.96</v>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>4.66</v>
+        <v>-1.84</v>
       </c>
       <c r="AN17" s="5" t="n">
         <v>0</v>
@@ -3238,14 +3262,14 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TER_USA_20260814</t>
+          <t>FOXA_USA_20260814</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -3265,7 +3289,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -3277,12 +3301,12 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -3290,10 +3314,10 @@
         </is>
       </c>
       <c r="O18" s="5" t="n">
-        <v>58.9</v>
+        <v>58.3</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
@@ -3302,12 +3326,12 @@
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr"/>
       <c r="T18" s="5" t="n">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
@@ -3315,7 +3339,7 @@
         </is>
       </c>
       <c r="V18" s="5" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="W18" s="5" t="inlineStr"/>
       <c r="X18" s="5" t="n">
@@ -3333,40 +3357,40 @@
         </is>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>410.52</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>410.52</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="AD18" s="5" t="n">
-        <v>402.31</v>
+        <v>68.38</v>
       </c>
       <c r="AE18" s="5" t="n">
-        <v>418.73</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="AF18" s="5" t="n">
-        <v>389.994</v>
+        <v>65.61649999999999</v>
       </c>
       <c r="AG18" s="5" t="n">
         <v>-5</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>443.3616</v>
+        <v>77.36</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>474.396912</v>
+        <v>82.7752</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AL18" s="5" t="n">
-        <v>402.74</v>
+        <v>65.45</v>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>1.93</v>
+        <v>5.53</v>
       </c>
       <c r="AN18" s="5" t="n">
         <v>0</v>
@@ -3387,18 +3411,18 @@
         <v>5</v>
       </c>
       <c r="AT18" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>CRM_USA_20260814</t>
+          <t>EIX_USA_20260814</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -3418,14 +3442,10 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -3434,12 +3454,12 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -3447,10 +3467,10 @@
         </is>
       </c>
       <c r="O19" s="5" t="n">
-        <v>60.6</v>
+        <v>61.4</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
@@ -3459,12 +3479,12 @@
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 61% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 62% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="n">
-        <v>60.6</v>
+        <v>62.2</v>
       </c>
       <c r="U19" s="5" t="inlineStr">
         <is>
@@ -3472,7 +3492,7 @@
         </is>
       </c>
       <c r="V19" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="W19" s="5" t="inlineStr"/>
       <c r="X19" s="5" t="n">
@@ -3490,40 +3510,40 @@
         </is>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>201.37</v>
+        <v>71.08</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>201.37</v>
+        <v>71.08</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>197.34</v>
+        <v>69.66</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>205.4</v>
+        <v>72.5</v>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>191.3015</v>
+        <v>67.526</v>
       </c>
       <c r="AG19" s="5" t="n">
         <v>-5</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>217.4796</v>
+        <v>76.7664</v>
       </c>
       <c r="AI19" s="5" t="n">
         <v>8</v>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>232.7031720000001</v>
+        <v>82.14004800000001</v>
       </c>
       <c r="AK19" s="5" t="n">
         <v>15.56</v>
       </c>
       <c r="AL19" s="5" t="n">
-        <v>193.32</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="AM19" s="5" t="n">
-        <v>4.16</v>
+        <v>0.57</v>
       </c>
       <c r="AN19" s="5" t="n">
         <v>0</v>
@@ -3548,779 +3568,739 @@
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>ADSK_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>UBER_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>ADSK</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="O20" s="7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="7" t="n">
         <v>59.1</v>
       </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="U20" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V20" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="5" t="n">
+      <c r="V20" s="7" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="W20" s="7" t="inlineStr"/>
+      <c r="X20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="Z20" s="5" t="n">
+      <c r="Z20" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="AA20" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB20" s="5" t="n">
-        <v>257.96</v>
-      </c>
-      <c r="AC20" s="5" t="n">
-        <v>257.96</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>255.38</v>
-      </c>
-      <c r="AE20" s="5" t="n">
-        <v>260.54</v>
-      </c>
-      <c r="AF20" s="5" t="n">
-        <v>245.062</v>
-      </c>
-      <c r="AG20" s="5" t="n">
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB20" s="7" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="AC20" s="7" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="AD20" s="7" t="n">
+        <v>73.91</v>
+      </c>
+      <c r="AE20" s="7" t="n">
+        <v>76.93000000000001</v>
+      </c>
+      <c r="AF20" s="7" t="n">
+        <v>71.649</v>
+      </c>
+      <c r="AG20" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AH20" s="5" t="n">
-        <v>288.92</v>
-      </c>
-      <c r="AI20" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ20" s="5" t="n">
-        <v>309.1444</v>
-      </c>
-      <c r="AK20" s="5" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="AL20" s="5" t="n">
-        <v>249.51</v>
-      </c>
-      <c r="AM20" s="5" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AN20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="5" t="inlineStr"/>
-      <c r="AR20" s="5" t="inlineStr">
+      <c r="AH20" s="7" t="n">
+        <v>81.45360000000001</v>
+      </c>
+      <c r="AI20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ20" s="7" t="n">
+        <v>87.15535200000001</v>
+      </c>
+      <c r="AK20" s="7" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL20" s="7" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AM20" s="7" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AN20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="7" t="inlineStr"/>
+      <c r="AR20" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AS20" s="5" t="n">
+      <c r="AS20" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AT20" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU20" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AT20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>BMY_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>CRM_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>BMY</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O21" s="5" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="O21" s="7" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 64% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="7" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V21" s="5" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="W21" s="5" t="inlineStr"/>
-      <c r="X21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="5" t="n">
+      <c r="V21" s="7" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W21" s="7" t="inlineStr"/>
+      <c r="X21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="Z21" s="5" t="n">
+      <c r="Z21" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="AA21" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB21" s="5" t="n">
-        <v>64.65000000000001</v>
-      </c>
-      <c r="AC21" s="5" t="n">
-        <v>64.65000000000001</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>63.36</v>
-      </c>
-      <c r="AE21" s="5" t="n">
-        <v>65.94</v>
-      </c>
-      <c r="AF21" s="5" t="n">
-        <v>61.4175</v>
-      </c>
-      <c r="AG21" s="5" t="n">
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB21" s="7" t="n">
+        <v>196.66</v>
+      </c>
+      <c r="AC21" s="7" t="n">
+        <v>196.66</v>
+      </c>
+      <c r="AD21" s="7" t="n">
+        <v>192.73</v>
+      </c>
+      <c r="AE21" s="7" t="n">
+        <v>200.59</v>
+      </c>
+      <c r="AF21" s="7" t="n">
+        <v>186.827</v>
+      </c>
+      <c r="AG21" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AH21" s="5" t="n">
-        <v>69.82200000000002</v>
-      </c>
-      <c r="AI21" s="5" t="n">
+      <c r="AH21" s="7" t="n">
+        <v>212.3928</v>
+      </c>
+      <c r="AI21" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AJ21" s="5" t="n">
-        <v>74.70954000000002</v>
-      </c>
-      <c r="AK21" s="5" t="n">
+      <c r="AJ21" s="7" t="n">
+        <v>227.260296</v>
+      </c>
+      <c r="AK21" s="7" t="n">
         <v>15.56</v>
       </c>
-      <c r="AL21" s="5" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="AM21" s="5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="5" t="inlineStr"/>
-      <c r="AR21" s="5" t="inlineStr">
+      <c r="AL21" s="7" t="n">
+        <v>201.37</v>
+      </c>
+      <c r="AM21" s="7" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="AN21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="7" t="inlineStr"/>
+      <c r="AR21" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AS21" s="5" t="n">
+      <c r="AS21" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AT21" s="5" t="n">
+      <c r="AT21" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AU21" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>FOXA_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>SMCI_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>FOXA</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="n">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.9%) · Rank #9 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr"/>
+      <c r="T22" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="W22" s="7" t="inlineStr"/>
+      <c r="X22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z22" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB22" s="7" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AC22" s="7" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AD22" s="7" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AE22" s="7" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="AF22" s="7" t="n">
+        <v>37.221</v>
+      </c>
+      <c r="AG22" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH22" s="7" t="n">
+        <v>42.3144</v>
+      </c>
+      <c r="AI22" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
-      <c r="X22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z22" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA22" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB22" s="5" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="AC22" s="5" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="AE22" s="5" t="n">
-        <v>66.76000000000001</v>
-      </c>
-      <c r="AF22" s="5" t="n">
-        <v>62.1775</v>
-      </c>
-      <c r="AG22" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH22" s="5" t="n">
-        <v>70.68600000000001</v>
-      </c>
-      <c r="AI22" s="5" t="n">
+      <c r="AJ22" s="7" t="n">
+        <v>45.276408</v>
+      </c>
+      <c r="AK22" s="7" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL22" s="7" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="AM22" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="7" t="inlineStr"/>
+      <c r="AR22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS22" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT22" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AJ22" s="5" t="n">
-        <v>75.63402000000001</v>
-      </c>
-      <c r="AK22" s="5" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AL22" s="5" t="n">
-        <v>63.05</v>
-      </c>
-      <c r="AM22" s="5" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AN22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="5" t="inlineStr"/>
-      <c r="AR22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT22" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU22" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>SMCI_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>SAIC_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>SMCI</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O23" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="O23" s="7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="P23" s="7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.9%) · Rank #9 · Conf 56% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="U23" s="5" t="inlineStr">
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr"/>
+      <c r="T23" s="7" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V23" s="5" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="W23" s="5" t="inlineStr"/>
-      <c r="X23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="5" t="n">
+      <c r="V23" s="7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="W23" s="7" t="inlineStr"/>
+      <c r="X23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="Z23" s="5" t="n">
+      <c r="Z23" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="AA23" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB23" s="5" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="AC23" s="5" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="AE23" s="5" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="AF23" s="5" t="n">
-        <v>37.202</v>
-      </c>
-      <c r="AG23" s="5" t="n">
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB23" s="7" t="n">
+        <v>125.89</v>
+      </c>
+      <c r="AC23" s="7" t="n">
+        <v>125.89</v>
+      </c>
+      <c r="AD23" s="7" t="n">
+        <v>123.37</v>
+      </c>
+      <c r="AE23" s="7" t="n">
+        <v>128.41</v>
+      </c>
+      <c r="AF23" s="7" t="n">
+        <v>119.5955</v>
+      </c>
+      <c r="AG23" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AH23" s="5" t="n">
-        <v>42.2928</v>
-      </c>
-      <c r="AI23" s="5" t="n">
+      <c r="AH23" s="7" t="n">
+        <v>135.9612</v>
+      </c>
+      <c r="AI23" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AJ23" s="5" t="n">
-        <v>45.253296</v>
-      </c>
-      <c r="AK23" s="5" t="n">
+      <c r="AJ23" s="7" t="n">
+        <v>145.478484</v>
+      </c>
+      <c r="AK23" s="7" t="n">
         <v>15.56</v>
       </c>
-      <c r="AL23" s="5" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="AM23" s="5" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AN23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="5" t="inlineStr"/>
-      <c r="AR23" s="5" t="inlineStr">
+      <c r="AL23" s="7" t="n">
+        <v>126.66</v>
+      </c>
+      <c r="AM23" s="7" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AN23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="7" t="inlineStr"/>
+      <c r="AR23" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AS23" s="5" t="n">
+      <c r="AS23" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AT23" s="5" t="n">
+      <c r="AT23" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AU23" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>SAIC_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260814</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 56% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="U24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr"/>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="7" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U24" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V24" s="5" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="W24" s="5" t="inlineStr"/>
-      <c r="X24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z24" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA24" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB24" s="5" t="n">
-        <v>126.66</v>
-      </c>
-      <c r="AC24" s="5" t="n">
-        <v>126.66</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>124.13</v>
-      </c>
-      <c r="AE24" s="5" t="n">
-        <v>129.19</v>
-      </c>
-      <c r="AF24" s="5" t="n">
-        <v>120.327</v>
-      </c>
-      <c r="AG24" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH24" s="5" t="n">
-        <v>136.7928</v>
-      </c>
-      <c r="AI24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ24" s="5" t="n">
-        <v>146.368296</v>
-      </c>
-      <c r="AK24" s="5" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AL24" s="5" t="n">
-        <v>126.31</v>
-      </c>
-      <c r="AM24" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AN24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="5" t="inlineStr"/>
-      <c r="AR24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS24" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU24" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+      <c r="V24" s="7" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="W24" s="7" t="inlineStr"/>
+      <c r="X24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z24" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA24" s="7" t="inlineStr"/>
+      <c r="AB24" s="7" t="inlineStr"/>
+      <c r="AC24" s="7" t="inlineStr"/>
+      <c r="AD24" s="7" t="inlineStr"/>
+      <c r="AE24" s="7" t="inlineStr"/>
+      <c r="AF24" s="7" t="inlineStr"/>
+      <c r="AG24" s="7" t="inlineStr"/>
+      <c r="AH24" s="7" t="inlineStr"/>
+      <c r="AI24" s="7" t="inlineStr"/>
+      <c r="AJ24" s="7" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr"/>
+      <c r="AL24" s="7" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM24" s="7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AN24" s="7" t="inlineStr"/>
+      <c r="AO24" s="7" t="inlineStr"/>
+      <c r="AP24" s="7" t="inlineStr"/>
+      <c r="AQ24" s="7" t="inlineStr"/>
+      <c r="AR24" s="7" t="inlineStr"/>
+      <c r="AS24" s="7" t="inlineStr"/>
+      <c r="AT24" s="7" t="inlineStr"/>
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>TRV_USA_20260814</t>
+          <t>V_USA_20260814</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -4340,12 +4320,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -4356,10 +4336,10 @@
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>0</v>
@@ -4371,12 +4351,12 @@
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr"/>
       <c r="T25" s="7" t="n">
-        <v>56.8</v>
+        <v>53.6</v>
       </c>
       <c r="U25" s="7" t="inlineStr">
         <is>
@@ -4384,7 +4364,7 @@
         </is>
       </c>
       <c r="V25" s="7" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="W25" s="7" t="inlineStr"/>
       <c r="X25" s="7" t="n">
@@ -4408,10 +4388,10 @@
       <c r="AJ25" s="7" t="inlineStr"/>
       <c r="AK25" s="7" t="inlineStr"/>
       <c r="AL25" s="7" t="n">
-        <v>370.16</v>
+        <v>365.45</v>
       </c>
       <c r="AM25" s="7" t="n">
-        <v>-0.04</v>
+        <v>-0.31</v>
       </c>
       <c r="AN25" s="7" t="inlineStr"/>
       <c r="AO25" s="7" t="inlineStr"/>
@@ -4422,121 +4402,12 @@
       <c r="AT25" s="7" t="inlineStr"/>
       <c r="AU25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14 13:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>V_USA_20260814</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-      <c r="J26" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-      <c r="O26" s="7" t="inlineStr"/>
-      <c r="P26" s="7" t="inlineStr"/>
-      <c r="Q26" s="7" t="inlineStr"/>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr"/>
-      <c r="T26" s="7" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W26" s="7" t="inlineStr"/>
-      <c r="X26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z26" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA26" s="7" t="inlineStr"/>
-      <c r="AB26" s="7" t="inlineStr"/>
-      <c r="AC26" s="7" t="inlineStr"/>
-      <c r="AD26" s="7" t="inlineStr"/>
-      <c r="AE26" s="7" t="inlineStr"/>
-      <c r="AF26" s="7" t="inlineStr"/>
-      <c r="AG26" s="7" t="inlineStr"/>
-      <c r="AH26" s="7" t="inlineStr"/>
-      <c r="AI26" s="7" t="inlineStr"/>
-      <c r="AJ26" s="7" t="inlineStr"/>
-      <c r="AK26" s="7" t="inlineStr"/>
-      <c r="AL26" s="7" t="n">
-        <v>359.42</v>
-      </c>
-      <c r="AM26" s="7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN26" s="7" t="inlineStr"/>
-      <c r="AO26" s="7" t="inlineStr"/>
-      <c r="AP26" s="7" t="inlineStr"/>
-      <c r="AQ26" s="7" t="inlineStr"/>
-      <c r="AR26" s="7" t="inlineStr"/>
-      <c r="AS26" s="7" t="inlineStr"/>
-      <c r="AT26" s="7" t="inlineStr"/>
-      <c r="AU26" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:23</t>
+          <t>2026-08-14 16:05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU26"/>
+  <autoFilter ref="A1:AU25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>